--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -5450,7 +5450,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>137172067</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137172068</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>137172069</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>137172070</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>137172071</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137172072</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>137172073</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>137172076</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137172077</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>137172078</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>137172079</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137172080</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137172081</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>137172082</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>137172083</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>137172084</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137172085</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>137172086</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>137172087</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>137172088</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137172089</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>137172090</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137172091</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>137172067</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137172068</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>137172069</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>137172070</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>137172071</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137172072</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>137172073</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>137172076</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>137172077</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>137172078</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>137172079</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>137172080</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137172081</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>137172082</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>137172083</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>137172084</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>137172085</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>137172086</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>137172087</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>137172088</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137172089</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>137172090</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137172091</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -2253,11 +2253,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2393,11 +2389,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2533,11 +2525,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2673,11 +2661,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2813,11 +2797,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2953,11 +2933,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3093,11 +3069,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3233,11 +3205,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3373,11 +3341,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3513,11 +3477,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3653,11 +3613,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3793,11 +3749,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3933,11 +3885,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4073,11 +4021,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4213,11 +4157,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4353,11 +4293,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4493,11 +4429,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4633,11 +4565,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4773,11 +4701,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4913,11 +4837,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5053,11 +4973,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5193,11 +5109,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5333,11 +5245,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5477,11 +5385,7 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -5598,11 +5502,7 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -5719,11 +5619,7 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -5835,11 +5731,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>137172067</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137172068</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137172069</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>137172070</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>137172071</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>137172072</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>137172073</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>137172076</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137172077</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>137172078</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>137172079</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>137172080</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>137172081</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137172082</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>137172083</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>137172084</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>137172085</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>137172086</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>137172087</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>137172088</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137172089</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>137172090</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137172091</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>137172067</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137172068</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137172069</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>137172070</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>137172071</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>137172072</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>137172073</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>137172076</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137172077</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>137172078</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>137172079</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>137172080</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>137172081</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137172082</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>137172083</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>137172084</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>137172085</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>137172086</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>137172087</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>137172088</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137172089</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>137172090</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137172091</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>137172067</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137172068</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137172069</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>137172070</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>137172071</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>137172072</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>137172073</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>137172076</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137172077</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>137172078</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>137172079</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>137172080</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>137172081</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137172082</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>137172083</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>137172084</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>137172085</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>137172086</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>137172087</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>137172088</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137172089</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>137172090</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137172091</v>
       </c>
       <c r="B36" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 58162-2025 artfynd.xlsx
+++ b/artfynd/A 58162-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172126</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172127</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137172128</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>137172129</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>137172130</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137172131</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137172132</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137172133</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>137172134</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>137172135</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137172136</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137172118</v>
       </c>
       <c r="B13" t="n">
-        <v>80654</v>
+        <v>80658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>137172067</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137172068</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137172069</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>137172070</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>137172071</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>137172072</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>137172073</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>137172076</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137172077</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>137172078</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>137172079</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>137172080</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>137172081</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137172082</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>137172083</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>137172084</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>137172085</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>137172086</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>137172087</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>137172088</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137172089</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>137172090</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137172091</v>
       </c>
       <c r="B36" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>137172151</v>
       </c>
       <c r="B37" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>137172152</v>
       </c>
       <c r="B38" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>137172123</v>
       </c>
       <c r="B39" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>137172124</v>
       </c>
       <c r="B40" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
